--- a/etf_holdings/2026-10-30_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00992A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.41%2415</t>
+          <t>-1.86%2370</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2415</v>
+        <v>2370</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.40%1,246,000</t>
+          <t>6.57%1,246,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.40%</t>
+          <t>6.57%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.42%3105</t>
+          <t>-0.32%3095</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3105</v>
+        <v>3095</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.27%921,000</t>
+          <t>6.24%921,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.45%1040</t>
+          <t>-4.9%989</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1040</v>
+        <v>989</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.25%2,682,000</t>
+          <t>6.09%2,682,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>6.09%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.52%1545</t>
+          <t>-7.12%1435</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1545</v>
+        <v>1435</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.85%1,743,000</t>
+          <t>5.88%1,743,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>5.88%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.31%1755</t>
+          <t>-6.69%4675</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>-6.69%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1755</v>
+        <v>4675</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.21%1,355,000</t>
+          <t>5.52%505,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1355000</v>
+        <v>505000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-5.8%1705</t>
+          <t>-7.98%1615</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-7.98%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1705</v>
+        <v>1615</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.14%1,341,000</t>
+          <t>5.19%1,355,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1341000</v>
+        <v>1355000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.3%5010</t>
+          <t>-4.69%1625</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5010</v>
+        <v>1625</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.47%420,000</t>
+          <t>4.99%1,341,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.99%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>420000</v>
+        <v>1341000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.21%5815</t>
+          <t>-6.62%5430</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.21%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5815</v>
+        <v>5430</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.33%323,000</t>
+          <t>4.10%323,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-5.38%4840</t>
+          <t>-2.33%9650</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4840</v>
+        <v>9650</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.94%364,000</t>
+          <t>3.95%183,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.94%</t>
+          <t>3.95%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>364000</v>
+        <v>183000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.66%9880</t>
+          <t>-4.75%4610</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9880</v>
+        <v>4610</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.93%183,000</t>
+          <t>3.84%364,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>3.84%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>183000</v>
+        <v>364000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.86%137</t>
+          <t>-7.66%126.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.86%</t>
+          <t>-7.66%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>137</v>
+        <v>126.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.85%12,620,868</t>
+          <t>3.77%12,620,868</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.19%312</t>
+          <t>-5.13%296</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-5.13%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.54%5,245,000</t>
+          <t>3.57%5,245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.57%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.49%7640</t>
+          <t>-0.07%7635</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.49%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7640</v>
+        <v>7635</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.50%202,000</t>
+          <t>3.37%202,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.37%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.85%1250</t>
+          <t>-4.8%1190</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1250</v>
+        <v>1190</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.19%1,157,000</t>
+          <t>3.16%1,157,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.19%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:28</t>
+          <t>2026-10-30 23:08:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-7.34%959</t>
+          <t>-2.82%932</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-7.34%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>959</v>
+        <v>932</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.92%1,334,013</t>
+          <t>2.79%1,334,013</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.5%428.5</t>
+          <t>-2.33%418.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>428.5</v>
+        <v>418.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.55%2,740,253</t>
+          <t>2.56%2,740,253</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-5.91%1115</t>
+          <t>-8.52%1020</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-8.52%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1115</v>
+        <v>1020</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.91%759,000</t>
+          <t>1.85%759,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-4.42%1945</t>
+          <t>-2.65%183.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1945</v>
+        <v>183.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.84%426,000</t>
+          <t>1.83%4,454,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>426000</v>
+        <v>4454000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.08%188.5</t>
+          <t>-3.98%1810</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>188.5</v>
+        <v>1810</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.83%4,454,000</t>
+          <t>1.81%440,675</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>4454000</v>
+        <v>440675</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-3.33%1885</t>
+          <t>-7.79%687</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-7.79%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1885</v>
+        <v>687</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.82%440,675</t>
+          <t>1.75%1,079,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>440675</v>
+        <v>1079000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-4.24%745</t>
+          <t>-9.77%1755</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>745</v>
+        <v>1755</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.78%1,079,000</t>
+          <t>1.75%413,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1079000</v>
+        <v>413000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.42%422</t>
+          <t>-3.08%409</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.76%1,884,000</t>
+          <t>1.73%1,884,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-4.49%4045</t>
+          <t>-8.99%1265</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.49%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>4045</v>
+        <v>1265</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.61%179,000</t>
+          <t>1.62%533,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>179000</v>
+        <v>533000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.09%1390</t>
+          <t>-3.21%3915</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1390</v>
+        <v>3915</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.55%533,000</t>
+          <t>1.58%179,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>533000</v>
+        <v>179000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-5.45%520</t>
+          <t>-6.54%486</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-6.54%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>520</v>
+        <v>486</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.40%1,200,000</t>
+          <t>1.36%1,200,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.82%16980</t>
+          <t>-5.95%15970</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>16980</v>
+        <v>15970</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.17%32,000</t>
+          <t>1.19%32,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.73%683</t>
+          <t>-2.2%668</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.11%755,000</t>
+          <t>1.13%755,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.47%6405</t>
+          <t>-1.41%6315</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6405</v>
+        <v>6315</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.93%69,000</t>
+          <t>0.96%69,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+2.13%767</t>
+          <t>-7.82%707</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-7.82%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>767</v>
+        <v>707</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.90%567,000</t>
+          <t>0.95%567,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:29</t>
+          <t>2026-10-30 23:08:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-6.32%1260</t>
+          <t>-7.96%2370</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6.32%</t>
+          <t>-7.96%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1260</v>
+        <v>2370</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.79%278,000</t>
+          <t>0.78%138,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>278000</v>
+        <v>138000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.19%2575</t>
+          <t>-5.56%1190</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2575</v>
+        <v>1190</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.75%138,000</t>
+          <t>0.76%278,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>138000</v>
+        <v>278000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6415矽力*-KY</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.52%1480</t>
+          <t>-4.2%502</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1480</v>
+        <v>502</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.66%200,000</t>
+          <t>0.67%590,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>200000</v>
+        <v>590000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-5.67%4655</t>
+          <t>-9.8%1335</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.67%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4655</v>
+        <v>1335</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.60%57,000</t>
+          <t>0.65%200,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>57000</v>
+        <v>200000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,34 +2517,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.19%665</t>
+          <t>-1.93%4565</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>665</v>
+        <v>4565</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.50%351,000</t>
+          <t>0.58%57,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>351000</v>
+        <v>57000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-3.28%97.2</t>
+          <t>-4.36%636</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-3.28%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>97.2</v>
+        <v>636</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.43%2,032,000</t>
+          <t>0.51%351,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2032000</v>
+        <v>351000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.85%950</t>
+          <t>-6.48%90.9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-6.48%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>950</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.43%206,000</t>
+          <t>0.43%2,032,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>206000</v>
+        <v>2032000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-5.38%343</t>
+          <t>-4.63%906</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>343</v>
+        <v>906</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.41%534,000</t>
+          <t>0.43%206,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>534000</v>
+        <v>206000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.45%1105</t>
+          <t>-2.71%1075</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1105</v>
+        <v>1075</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.39%166,000</t>
+          <t>0.40%166,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,34 +2822,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.63%252</t>
+          <t>-2.04%336</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>252</v>
+        <v>336</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.38%693,000</t>
+          <t>0.40%534,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>693000</v>
+        <v>534000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>-5.08%1120</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1180</v>
+        <v>1120</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.38%152,952</t>
+          <t>0.39%152,952</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.42%236.5</t>
+          <t>-4.56%240.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-4.56%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>236.5</v>
+        <v>240.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.25%500,000</t>
+          <t>0.38%693,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>500000</v>
+        <v>693000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-6.57%156.5</t>
+          <t>-6.77%220.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.57%</t>
+          <t>-6.77%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>156.5</v>
+        <v>220.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.22%629,000</t>
+          <t>0.26%500,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>629000</v>
+        <v>500000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:31</t>
+          <t>2026-10-30 23:08:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,41 +3066,102 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>5347世界</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-7.99%144</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-7.99%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>144</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.21%629,000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>629000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-30 23:08:45</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>3131弘塑</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-3.85%2000</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-3.85%</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I44" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-6%1880</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-6%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1880</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>&lt;0.01%1,000</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>&lt;0.01%</t>
         </is>
       </c>
-      <c r="K44" t="n">
+      <c r="K45" t="n">
         <v>1000</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-0.00%</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-30_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:43</t>
+          <t>2026-10-30 23:20:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:44</t>
+          <t>2026-10-30 23:20:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:45</t>
+          <t>2026-10-30 23:20:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">

--- a/etf_holdings/2026-10-30_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:26</t>
+          <t>2026-10-30 23:56:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:28</t>
+          <t>2026-10-30 23:56:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:29</t>
+          <t>2026-10-30 23:56:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
